--- a/Documentation/RTM - WorkForcePro.xlsx
+++ b/Documentation/RTM - WorkForcePro.xlsx
@@ -253,7 +253,7 @@
     <t>RTM -18</t>
   </si>
   <si>
-    <t>Validate complete business workflow</t>
+    <t>Validate end to end business workflow</t>
   </si>
   <si>
     <t>TS-E2E-001, TS-E2E-002, TS-E2E-003</t>
